--- a/data/proteomics/membrance_size_across_go_term_Rosemary.xlsx
+++ b/data/proteomics/membrance_size_across_go_term_Rosemary.xlsx
@@ -4823,58 +4823,58 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3.753927919367932</v>
+        <v>3.259494961136097</v>
       </c>
       <c r="D69" t="n">
-        <v>3.32120308969014</v>
+        <v>2.904343539622074</v>
       </c>
       <c r="E69" t="n">
-        <v>3.699916490141849</v>
+        <v>3.155426648617012</v>
       </c>
       <c r="F69" t="n">
-        <v>3.129534818587946</v>
+        <v>2.674410557102173</v>
       </c>
       <c r="G69" t="n">
-        <v>3.301382109513384</v>
+        <v>2.8447215370122</v>
       </c>
       <c r="H69" t="n">
-        <v>4.955432341851611</v>
+        <v>4.179675431125347</v>
       </c>
       <c r="I69" t="n">
-        <v>5.19614072955638</v>
+        <v>4.485683133397495</v>
       </c>
       <c r="J69" t="n">
-        <v>4.527106779856688</v>
+        <v>3.871151530405819</v>
       </c>
       <c r="K69" t="n">
-        <v>4.491229001465156</v>
+        <v>3.866806935252488</v>
       </c>
       <c r="L69" t="n">
-        <v>5.278623349859647</v>
+        <v>4.572841030067726</v>
       </c>
       <c r="M69" t="n">
-        <v>5.339189493420673</v>
+        <v>4.544008080648103</v>
       </c>
       <c r="N69" t="n">
-        <v>5.238974684961763</v>
+        <v>4.504023970914154</v>
       </c>
       <c r="O69" t="n">
-        <v>10.08550445753291</v>
+        <v>8.693505063317348</v>
       </c>
       <c r="P69" t="n">
-        <v>10.25395193273789</v>
+        <v>8.772429087084685</v>
       </c>
       <c r="Q69" t="n">
-        <v>9.288664702310928</v>
+        <v>7.792615458626454</v>
       </c>
       <c r="R69" t="n">
-        <v>13.85584720491891</v>
+        <v>11.78151189765948</v>
       </c>
       <c r="S69" t="n">
-        <v>15.09010153488797</v>
+        <v>12.94549111718702</v>
       </c>
       <c r="T69" t="n">
-        <v>14.04798658105224</v>
+        <v>12.0570928146099</v>
       </c>
     </row>
     <row r="70">
